--- a/BOM/BOM.xlsx
+++ b/BOM/BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\marinboard\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE498B0-1EE6-4E0D-AF50-344C59DE315E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383630E1-298A-4799-AD0B-112B88C4C889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5803721C-F8C9-41F6-8A44-40A526ECC638}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -78,6 +78,24 @@
   </si>
   <si>
     <t>total</t>
+  </si>
+  <si>
+    <t>cherry mx switches</t>
+  </si>
+  <si>
+    <t>11.56$</t>
+  </si>
+  <si>
+    <t>7.52$</t>
+  </si>
+  <si>
+    <t>https://www.temu.com/goods.html?_bg_fs=1&amp;goods_id=607310772554699&amp;sku_id=106093476892819&amp;_oak_page_source=501&amp;_x_vst_scene=adg&amp;_x_ads_sub_channel=shopping&amp;_x_ns_prz_type=-1&amp;_x_ns_sku_id=17610262579849&amp;_x_ns_gid=601103526355017&amp;_x_ads_channel=google&amp;_x_gmc_account=5583670251&amp;_x_login_type=Google&amp;_x_ns_gg_lnk_type=adr&amp;_x_ads_account=8024674409&amp;_x_ads_set=22727257096&amp;_x_ads_id=181916663215&amp;_x_ads_creative_id=760739761169&amp;_x_ns_source=g&amp;_x_ns_gclid=EAIaIQobChMIyPORhJKMlwMV36SDBx2tuQBiEAQYAyABEgIREPD_BwE&amp;_x_ns_placement=&amp;_x_ns_match_type=&amp;_x_ns_ad_position=&amp;_x_ns_product_id=5583670251-17610262579849&amp;_x_ns_target=&amp;_x_ns_devicemodel=&amp;_x_ns_wbraid=Cj4KCAjwt9jVBhAnEi4ALlmaWz3Ng_r9wC83DnMv7dgZEF512HbIaQWrrpXrc3PSBd1ZPGtcmkN-AGrgGgK0gA&amp;_x_ns_gbraid=0AAAAAo4mICF9jYkoASpfWJisz63sOpxNO&amp;_x_ns_targetid=pla-2429506025240&amp;_x_sessn_id=6g1a3zda1n&amp;refer_page_name=shopping_cart&amp;refer_page_id=10037_1790422315319_c2v1kjvsyh&amp;refer_page_sn=10037</t>
+  </si>
+  <si>
+    <t>keycaps</t>
+  </si>
+  <si>
+    <t>https://www.temu.com/goods.html?_bg_fs=1&amp;goods_id=601099762575194&amp;sku_id=17593185631687&amp;_oak_page_source=501&amp;_x_ns_irclickid=U--xYnyxOxyKT%3AwQynQ-IWN1UkrzhcwM21kZUw0&amp;_x_ads_account=18350&amp;_x_ads_id=1580294&amp;_x_ns_iradname=Online%2BTracking%2BLink&amp;_x_ns_iradsize=&amp;_x_ns_prodsku=&amp;_x_ns_irmptype=mediapartner&amp;_x_ns_sharedid=&amp;_x_ns_ts=1789813578175&amp;_x_ns_randint=9724412&amp;_x_ns_adtype=ONLINE_TRACKING_LINK&amp;_x_ns_irmpgroupname="ld"%2C"US"&amp;_x_ads_channel=impact&amp;_x_ns_mp_value2=&amp;_x_ns_mp_value3=&amp;_x_ns_irmpname=Opera%E2%80%8A&amp;_x_ns_irpid=1943907&amp;_x_vst_scene=adg&amp;_x_sessn_id=80e3cu2gu0&amp;refer_page_name=shopping_cart&amp;refer_page_id=10037_1790422392073_kwofvvozaw&amp;refer_page_sn=10037</t>
   </si>
 </sst>
 </file>
@@ -464,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DBF5900-5AB9-48A9-B375-19E77B9C61D7}">
-  <dimension ref="B4:D9"/>
+  <dimension ref="B4:D12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="35.5703125" customWidth="1"/>
@@ -525,11 +543,33 @@
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="2">
-        <f>31.2+2.06+9.29+7.9</f>
-        <v>50.449999999999996</v>
+      <c r="C12">
+        <f>7.52+11.56+31.2+2.06+9.29+7.9</f>
+        <v>69.53</v>
       </c>
     </row>
   </sheetData>

--- a/BOM/BOM.xlsx
+++ b/BOM/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\marinboard\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383630E1-298A-4799-AD0B-112B88C4C889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4812F401-6AA1-4E5D-97FD-D8F74A33C3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5803721C-F8C9-41F6-8A44-40A526ECC638}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -96,6 +96,15 @@
   </si>
   <si>
     <t>https://www.temu.com/goods.html?_bg_fs=1&amp;goods_id=601099762575194&amp;sku_id=17593185631687&amp;_oak_page_source=501&amp;_x_ns_irclickid=U--xYnyxOxyKT%3AwQynQ-IWN1UkrzhcwM21kZUw0&amp;_x_ads_account=18350&amp;_x_ads_id=1580294&amp;_x_ns_iradname=Online%2BTracking%2BLink&amp;_x_ns_iradsize=&amp;_x_ns_prodsku=&amp;_x_ns_irmptype=mediapartner&amp;_x_ns_sharedid=&amp;_x_ns_ts=1789813578175&amp;_x_ns_randint=9724412&amp;_x_ns_adtype=ONLINE_TRACKING_LINK&amp;_x_ns_irmpgroupname="ld"%2C"US"&amp;_x_ads_channel=impact&amp;_x_ns_mp_value2=&amp;_x_ns_mp_value3=&amp;_x_ns_irmpname=Opera%E2%80%8A&amp;_x_ns_irpid=1943907&amp;_x_vst_scene=adg&amp;_x_sessn_id=80e3cu2gu0&amp;refer_page_name=shopping_cart&amp;refer_page_id=10037_1790422392073_kwofvvozaw&amp;refer_page_sn=10037</t>
+  </si>
+  <si>
+    <t>6,57 $</t>
+  </si>
+  <si>
+    <t>https://www.temu.com/goods.html?_bg_fs=1&amp;goods_id=601099714384815&amp;sku_id=17592968516016&amp;_oak_page_source=501&amp;_x_vst_scene=adg&amp;_x_ads_sub_channel=shopping&amp;_x_ns_prz_type=-1&amp;_x_ns_sku_id=103956529309043&amp;_x_ns_gid=605839159071835&amp;_x_ads_channel=google&amp;_x_gmc_account=5583670251&amp;_x_login_type=Google&amp;_x_ns_gg_lnk_type=adr&amp;_x_ads_account=8024674409&amp;_x_ads_set=22727250607&amp;_x_ads_id=181267915843&amp;_x_ads_creative_id=760739782520&amp;_x_ns_source=g&amp;_x_ns_gclid=EAIaIQobChMI8ruj5pSMlwMVqzUGAB1HngE_EAkYBCABEgJhKvD_BwE&amp;_x_ns_placement=&amp;_x_ns_match_type=&amp;_x_ns_ad_position=&amp;_x_ns_product_id=5583670251-103956529309043&amp;_x_ns_target=&amp;_x_ns_devicemodel=&amp;_x_ns_wbraid=Cj4KCAjwt9jVBhAnEi4ALlmaW4HmASogvilFUBs56sKgn88b3uuC4qlvRsTIXzqQF1KZaVkoK4C680EpGgLC9g&amp;_x_ns_gbraid=0AAAAAo4mICFR86NDoyZ_xToHQhp88cJPN&amp;_x_ns_targetid=pla-2430213309551&amp;_x_sessn_id=wzmsw33540&amp;refer_page_name=shopping_cart&amp;refer_page_id=10037_1790423100556_hmi6s4f9b0&amp;refer_page_sn=10037</t>
+  </si>
+  <si>
+    <t>knurled nuts brass m3</t>
   </si>
 </sst>
 </file>
@@ -563,13 +572,24 @@
         <v>18</v>
       </c>
     </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12">
-        <f>7.52+11.56+31.2+2.06+9.29+7.9</f>
-        <v>69.53</v>
+        <f>6.57+7.52+11.56+31.2+2.06+9.29+7.9</f>
+        <v>76.099999999999994</v>
       </c>
     </row>
   </sheetData>

--- a/BOM/BOM.xlsx
+++ b/BOM/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\marinboard\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4812F401-6AA1-4E5D-97FD-D8F74A33C3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A742A81-FCCB-460F-82FB-CF35A654A948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5803721C-F8C9-41F6-8A44-40A526ECC638}"/>
   </bookViews>
@@ -547,7 +547,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="2">
-        <v>31.2</v>
+        <v>69.28</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
@@ -588,8 +588,8 @@
         <v>12</v>
       </c>
       <c r="C12">
-        <f>6.57+7.52+11.56+31.2+2.06+9.29+7.9</f>
-        <v>76.099999999999994</v>
+        <f>6.57+7.52+11.56+69.28+2.06+9.29+7.9</f>
+        <v>114.18</v>
       </c>
     </row>
   </sheetData>
